--- a/reTIME/data.xlsx
+++ b/reTIME/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DE TAI CO SO\2026\APP\reTIME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7488E515-5488-48E9-90A5-ABC807A3E0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD632D-E054-4372-95A9-F2AA88B375E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="90">
   <si>
     <t>Ma_Thu_Thuat</t>
   </si>
@@ -250,6 +250,48 @@
   </si>
   <si>
     <t>LASER CST</t>
+  </si>
+  <si>
+    <t>TT12</t>
+  </si>
+  <si>
+    <t>HỒNG NGOẠI</t>
+  </si>
+  <si>
+    <t>Máy hồng ngoại</t>
+  </si>
+  <si>
+    <t>TT13</t>
+  </si>
+  <si>
+    <t>LASER NỘI MẠCH</t>
+  </si>
+  <si>
+    <t>Máy Laser NM</t>
+  </si>
+  <si>
+    <t>TT14</t>
+  </si>
+  <si>
+    <t>BẤM HUYỆT</t>
+  </si>
+  <si>
+    <t>TT15</t>
+  </si>
+  <si>
+    <t>PARAFIN</t>
+  </si>
+  <si>
+    <t>Máy Parafin</t>
+  </si>
+  <si>
+    <t>TT16</t>
+  </si>
+  <si>
+    <t>SÓNG NGẮN</t>
+  </si>
+  <si>
+    <t>Máy sóng ngắn</t>
   </si>
 </sst>
 </file>
@@ -543,7 +585,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -829,6 +871,121 @@
       </c>
       <c r="G12" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="1">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
